--- a/quizzes/009_smartphone_consumer_behavior_quiz--quizzes.xlsx
+++ b/quizzes/009_smartphone_consumer_behavior_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your average monthly spend on phone bills?</t>
+          <t>Smartphone Consumer Behavior Quiz 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is your average monthly spend on phone bills?</t>
+          <t>Smartphone Consumer Behavior Quiz 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How often do you use your phone's camera?</t>
+          <t>Smartphone Consumer Behavior Quiz 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
